--- a/design/MiniTemplate/Excels/#achieve.xlsx
+++ b/design/MiniTemplate/Excels/#achieve.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\BiliBili\Work\slime\design\MiniTemplate\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6097DB95-89E4-4322-9B07-C3A8985A347F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C143BCB-0ED1-44DE-8B34-DD2409F9AEDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="99">
   <si>
     <t>##var</t>
   </si>
@@ -254,9 +254,6 @@
     <t>奖励:随机图鉴解锁</t>
   </si>
   <si>
-    <t>max</t>
-  </si>
-  <si>
     <t>奖励:最大等级+10</t>
   </si>
   <si>
@@ -272,6 +269,76 @@
   <si>
     <t>boss</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>h129</t>
+  </si>
+  <si>
+    <t>h105</t>
+  </si>
+  <si>
+    <t>h88</t>
+  </si>
+  <si>
+    <t>h3</t>
+  </si>
+  <si>
+    <t>h31</t>
+  </si>
+  <si>
+    <t>h87</t>
+  </si>
+  <si>
+    <t>h139</t>
+  </si>
+  <si>
+    <t>h101</t>
+  </si>
+  <si>
+    <t>h79</t>
+  </si>
+  <si>
+    <t>h125</t>
+  </si>
+  <si>
+    <t>h140</t>
+  </si>
+  <si>
+    <t>h48</t>
+  </si>
+  <si>
+    <t>h11</t>
+  </si>
+  <si>
+    <t>h35</t>
+  </si>
+  <si>
+    <t>h27</t>
+  </si>
+  <si>
+    <t>h44</t>
+  </si>
+  <si>
+    <t>h52</t>
+  </si>
+  <si>
+    <t>b1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>b2</t>
+  </si>
+  <si>
+    <t>b3</t>
+  </si>
+  <si>
+    <t>b4</t>
+  </si>
+  <si>
+    <t>b5</t>
   </si>
 </sst>
 </file>
@@ -861,10 +928,10 @@
         <v>24</v>
       </c>
       <c r="G9" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -901,10 +968,10 @@
         <v>26</v>
       </c>
       <c r="G11" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -941,10 +1008,10 @@
         <v>28</v>
       </c>
       <c r="G13" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -981,10 +1048,10 @@
         <v>30</v>
       </c>
       <c r="G15" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H15" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1021,10 +1088,10 @@
         <v>32</v>
       </c>
       <c r="G17" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H17" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
@@ -1061,10 +1128,10 @@
         <v>34</v>
       </c>
       <c r="G19" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H19" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
@@ -1101,10 +1168,10 @@
         <v>36</v>
       </c>
       <c r="G21" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H21" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
@@ -1141,10 +1208,10 @@
         <v>38</v>
       </c>
       <c r="G23" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
@@ -1174,8 +1241,8 @@
       <c r="C25" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D25" s="1">
-        <v>129</v>
+      <c r="D25" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="E25" s="1">
         <v>20</v>
@@ -1197,8 +1264,8 @@
       <c r="C26" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D26" s="1">
-        <v>105</v>
+      <c r="D26" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="E26" s="1">
         <v>20</v>
@@ -1220,8 +1287,8 @@
       <c r="C27" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D27" s="1">
-        <v>88</v>
+      <c r="D27" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="E27" s="1">
         <v>20</v>
@@ -1243,8 +1310,8 @@
       <c r="C28" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D28" s="1">
-        <v>3</v>
+      <c r="D28" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="E28" s="1">
         <v>10</v>
@@ -1266,8 +1333,8 @@
       <c r="C29" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D29" s="1">
-        <v>31</v>
+      <c r="D29" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="E29" s="1">
         <v>10</v>
@@ -1289,8 +1356,8 @@
       <c r="C30" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D30" s="1">
-        <v>87</v>
+      <c r="D30" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="E30" s="1">
         <v>10</v>
@@ -1312,8 +1379,8 @@
       <c r="C31" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D31" s="1">
-        <v>139</v>
+      <c r="D31" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="E31" s="1">
         <v>5</v>
@@ -1335,8 +1402,8 @@
       <c r="C32" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D32" s="1">
-        <v>101</v>
+      <c r="D32" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="E32" s="1">
         <v>5</v>
@@ -1358,8 +1425,8 @@
       <c r="C33" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D33" s="1">
-        <v>79</v>
+      <c r="D33" s="1" t="s">
+        <v>85</v>
       </c>
       <c r="E33" s="1">
         <v>5</v>
@@ -1381,8 +1448,8 @@
       <c r="C34" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D34" s="1">
-        <v>125</v>
+      <c r="D34" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="E34" s="1">
         <v>2</v>
@@ -1404,8 +1471,8 @@
       <c r="C35" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D35" s="1">
-        <v>140</v>
+      <c r="D35" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="E35" s="1">
         <v>2</v>
@@ -1427,8 +1494,8 @@
       <c r="C36" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D36" s="1">
-        <v>48</v>
+      <c r="D36" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="E36" s="1">
         <v>2</v>
@@ -1450,8 +1517,8 @@
       <c r="C37" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D37" s="1">
-        <v>11</v>
+      <c r="D37" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
@@ -1473,8 +1540,8 @@
       <c r="C38" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D38" s="1">
-        <v>35</v>
+      <c r="D38" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
@@ -1496,8 +1563,8 @@
       <c r="C39" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D39" s="1">
-        <v>27</v>
+      <c r="D39" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
@@ -1519,8 +1586,8 @@
       <c r="C40" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D40" s="1">
-        <v>44</v>
+      <c r="D40" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="E40" s="1">
         <v>1</v>
@@ -1542,8 +1609,8 @@
       <c r="C41" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D41" s="1">
-        <v>52</v>
+      <c r="D41" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="E41" s="1">
         <v>1</v>
@@ -1572,10 +1639,10 @@
         <v>57</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.25">
@@ -1592,10 +1659,10 @@
         <v>58</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.25">
@@ -1612,10 +1679,10 @@
         <v>59</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.25">
@@ -1625,8 +1692,8 @@
       <c r="C45" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D45" s="1">
-        <v>141</v>
+      <c r="D45" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="E45" s="1">
         <v>1</v>
@@ -1635,10 +1702,10 @@
         <v>60</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.25">
@@ -1648,8 +1715,8 @@
       <c r="C46" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D46" s="1">
-        <v>142</v>
+      <c r="D46" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="E46" s="1">
         <v>1</v>
@@ -1671,8 +1738,8 @@
       <c r="C47" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D47" s="1">
-        <v>143</v>
+      <c r="D47" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="E47" s="1">
         <v>1</v>
@@ -1681,10 +1748,10 @@
         <v>62</v>
       </c>
       <c r="G47" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H47" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.25">
@@ -1694,8 +1761,8 @@
       <c r="C48" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D48" s="1">
-        <v>144</v>
+      <c r="D48" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="E48" s="1">
         <v>1</v>
@@ -1704,10 +1771,10 @@
         <v>63</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.25">
@@ -1717,8 +1784,8 @@
       <c r="C49" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D49" s="1">
-        <v>145</v>
+      <c r="D49" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="E49" s="1">
         <v>1</v>
@@ -1727,10 +1794,10 @@
         <v>64</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
